--- a/Banking_Stress_Testing_2024.xlsx
+++ b/Banking_Stress_Testing_2024.xlsx
@@ -7,81 +7,69 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
-    <sheet name="Rate_Shock_Losses" sheetId="2" r:id="rId2"/>
-    <sheet name="Liquidity_Summary" sheetId="3" r:id="rId3"/>
-    <sheet name="Interbank_Exposure (bn)" sheetId="4" r:id="rId4"/>
-    <sheet name="Spillover_Rounds" sheetId="5" r:id="rId5"/>
-    <sheet name="Summary" sheetId="6" r:id="rId6"/>
+    <sheet name="Liquidity_Stress" sheetId="1" r:id="rId1"/>
+    <sheet name="Bond_Losses" sheetId="2" r:id="rId2"/>
+    <sheet name="Contagion_Simulation" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="28">
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Starting CET1 Capital</t>
-  </si>
-  <si>
-    <t>AFS Securities (market value)</t>
-  </si>
-  <si>
-    <t>HTM Securities (amortized cost)</t>
-  </si>
-  <si>
-    <t>AFS Duration (yrs)</t>
-  </si>
-  <si>
-    <t>HTM Duration (yrs)</t>
-  </si>
-  <si>
-    <t>Liquidity Buffer (HQLA)</t>
-  </si>
-  <si>
-    <t>Deposit Base</t>
-  </si>
-  <si>
-    <t>Liquidity Haircut (%)</t>
-  </si>
-  <si>
-    <t>Stress Horizon (days)</t>
-  </si>
-  <si>
-    <t>Rate Shock (bps)</t>
-  </si>
-  <si>
-    <t>AFS Loss ($)</t>
-  </si>
-  <si>
-    <t>HTM Econ Loss ($)</t>
-  </si>
-  <si>
-    <t>CET1 Hit (%)</t>
-  </si>
-  <si>
-    <t>Econ CET1 Hit (%)</t>
-  </si>
-  <si>
-    <t>Outflow / Day (%)</t>
-  </si>
-  <si>
-    <t>Days Survived</t>
-  </si>
-  <si>
-    <t>End HQLA ($)</t>
-  </si>
-  <si>
-    <t>Bank A</t>
-  </si>
-  <si>
-    <t>Bank B</t>
-  </si>
-  <si>
-    <t>Bank C</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+  <si>
+    <t>SVB</t>
+  </si>
+  <si>
+    <t>Credit Suisse</t>
+  </si>
+  <si>
+    <t>Regional Avg</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>0.00%</t>
+  </si>
+  <si>
+    <t>0.25%</t>
+  </si>
+  <si>
+    <t>0.50%</t>
+  </si>
+  <si>
+    <t>0.75%</t>
+  </si>
+  <si>
+    <t>1.00%</t>
+  </si>
+  <si>
+    <t>1.25%</t>
+  </si>
+  <si>
+    <t>1.50%</t>
+  </si>
+  <si>
+    <t>1.75%</t>
+  </si>
+  <si>
+    <t>2.00%</t>
+  </si>
+  <si>
+    <t>Rate Shock (%)</t>
+  </si>
+  <si>
+    <t>1Y</t>
+  </si>
+  <si>
+    <t>2Y</t>
+  </si>
+  <si>
+    <t>5Y</t>
+  </si>
+  <si>
+    <t>10Y</t>
   </si>
   <si>
     <t>Round</t>
@@ -90,19 +78,25 @@
     <t>Bank</t>
   </si>
   <si>
-    <t>Loss (bn)</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Max CET1 Hit (%)</t>
-  </si>
-  <si>
-    <t>Avg Liquidity Days Survived</t>
-  </si>
-  <si>
-    <t>Max Interbank Loss (bn)</t>
+    <t>Losses</t>
+  </si>
+  <si>
+    <t>Defaulted</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
   </si>
 </sst>
 </file>
@@ -126,18 +120,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -167,12 +155,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -197,7 +184,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Liquidity Survival vs Outflow Rate</a:t>
+              <a:t>Liquidity Stress — Deposit Outflows</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -206,61 +193,660 @@
     </c:title>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Days Survived</c:v>
+            <c:strRef>
+              <c:f>Liquidity_Stress!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SVB</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Liquidity_Summary!$A$2:$A$5</c:f>
+              <c:f>Liquidity_Stress!$A$2:$A$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.5</c:v>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.5</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2</c:v>
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Liquidity_Summary!$B$2:$B$5</c:f>
+              <c:f>Liquidity_Stress!$B$2:$B$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>30</c:v>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>2.29802849180674</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24</c:v>
+                  <c:v>4.215069911104029</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16</c:v>
+                  <c:v>6.603683033964445</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12</c:v>
+                  <c:v>9.51750094780926</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11.37700892297526</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>13.23652674880575</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16.18405443811019</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18.64451527560193</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20.36283064404096</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>22.68836667019254</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>24.41031605450506</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>26.13087820236291</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>28.27605556530253</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>29.12808741850785</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>30.09313671900003</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>31.75576420145545</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>33.14806552925479</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>35.33661392881196</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>36.79179948349923</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>37.94441726269806</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>40.82380652405099</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>42.68834074375907</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>44.72885766657183</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>45.87400875484375</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>47.54737912012864</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>49.61393267395456</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>50.92333652750118</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>53.14875533850858</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>54.7883721245573</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>56.61335587468133</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
         </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Liquidity_Stress!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Credit Suisse</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Liquidity_Stress!$A$2:$A$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Liquidity_Stress!$C$2:$C$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>0.8991466938853014</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.02528578613977</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.218537173770804</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.889681709292853</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.500954165344448</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.090532340358936</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.394964137861313</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.615129075921425</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.151036051472209</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10.44946666940677</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12.01869995940448</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>13.30438409999946</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>14.44655995880534</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15.4960081110107</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15.95674711582698</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16.79682501162963</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17.76650562614974</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19.49506673925919</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>20.86687588404342</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>21.18535580636206</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>22.54739779105946</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>23.5548566508513</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>24.41639565069832</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>25.92223379511875</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>27.63773355636673</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>29.30337361592483</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>30.08376485431351</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>31.12915866638791</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>32.49479038208969</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>34.18256294565087</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Liquidity_Stress!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Regional Avg</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Liquidity_Stress!$A$2:$A$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Liquidity_Stress!$D$2:$D$31</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>0.3041651524309421</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.6670333570981786</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.8457663622969729</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.006525037480839</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.569030201959678</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.240278207673843</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.625876183357776</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.226582762936181</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.698909967945708</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.969886017024683</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.442165138126366</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.14977245141956</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.54260724359757</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.255535974760371</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.131586953942422</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6.695967454817467</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.113376868465101</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7.453575398371928</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7.871927553679028</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>7.874413770758849</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>8.230479393191347</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>8.701901907493696</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>9.397480716441999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>9.693826672787269</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>9.932127952208631</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>10.23177654349172</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>10.81485696703214</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>11.28060718896408</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>11.57465514821067</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>12.07730863483334</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:marker val="1"/>
         <c:axId val="50010001"/>
         <c:axId val="50010002"/>
-      </c:barChart>
+      </c:lineChart>
       <c:catAx>
         <c:axId val="50010001"/>
         <c:scaling>
@@ -318,7 +904,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>CET1 Hit vs Rate Shock</a:t>
+              <a:t>Bond Portfolio Losses vs Rate Shocks</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -333,61 +919,528 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>CET1 Hit (%)</c:v>
+            <c:strRef>
+              <c:f>Bond_Losses!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.00%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:numRef>
-              <c:f>Rate_Shock_Losses!$A$2:$A$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>50</c:v>
+            <c:strRef>
+              <c:f>Bond_Losses!$A$2:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1Y</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>100</c:v>
+                  <c:v>2Y</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>150</c:v>
+                  <c:v>5Y</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>200</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>300</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>400</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>10Y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Rate_Shock_Losses!$D$2:$D$7</c:f>
+              <c:f>Bond_Losses!$B$2:$B$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>11.52</c:v>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>-0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>23.04</c:v>
+                  <c:v>-0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>34.56</c:v>
+                  <c:v>-0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46.08</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>69.12</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>92.16</c:v>
+                  <c:v>-0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Bond_Losses!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.25%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Bond_Losses!$A$2:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1Y</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2Y</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5Y</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10Y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Bond_Losses!$C$2:$C$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>-0.0025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.005</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.0125</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.025</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Bond_Losses!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.50%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Bond_Losses!$A$2:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1Y</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2Y</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5Y</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10Y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Bond_Losses!$D$2:$D$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>-0.005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.05</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Bond_Losses!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.75%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Bond_Losses!$A$2:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1Y</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2Y</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5Y</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10Y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Bond_Losses!$E$2:$E$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>-0.0075</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.015</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.0375</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.075</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Bond_Losses!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.00%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Bond_Losses!$A$2:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1Y</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2Y</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5Y</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10Y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Bond_Losses!$F$2:$F$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>-0.01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.05</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Bond_Losses!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.25%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Bond_Losses!$A$2:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1Y</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2Y</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5Y</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10Y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Bond_Losses!$G$2:$G$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>-0.0125</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.025</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.0625</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.125</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Bond_Losses!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.50%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Bond_Losses!$A$2:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1Y</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2Y</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5Y</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10Y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Bond_Losses!$H$2:$H$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>-0.015</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.03</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.075</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Bond_Losses!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.75%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Bond_Losses!$A$2:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1Y</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2Y</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5Y</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10Y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Bond_Losses!$I$2:$I$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>-0.0175</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.035</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.08749999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.175</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Bond_Losses!$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.00%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Bond_Losses!$A$2:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1Y</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2Y</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5Y</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10Y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Bond_Losses!$J$2:$J$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>-0.02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-0.04</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -403,7 +1456,24 @@
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Rate Shock (%)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020002"/>
         <c:crosses val="autoZero"/>
@@ -418,6 +1488,24 @@
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Portfolio Loss (%)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020001"/>
@@ -443,13 +1531,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
@@ -478,13 +1566,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
@@ -794,278 +1882,441 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
       <c r="B2">
-        <v>25000000000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
+        <v>2.29802849180674</v>
+      </c>
+      <c r="C2">
+        <v>0.8991466938853014</v>
+      </c>
+      <c r="D2">
+        <v>0.3041651524309421</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>180000000000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
+        <v>4.215069911104029</v>
+      </c>
+      <c r="C3">
+        <v>3.02528578613977</v>
+      </c>
+      <c r="D3">
+        <v>0.6670333570981786</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>100000000000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
+        <v>6.603683033964445</v>
+      </c>
+      <c r="C4">
+        <v>4.218537173770804</v>
+      </c>
+      <c r="D4">
+        <v>0.8457663622969729</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
+        <v>9.51750094780926</v>
+      </c>
+      <c r="C5">
+        <v>4.889681709292853</v>
+      </c>
+      <c r="D5">
+        <v>1.006525037480839</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6">
+        <v>11.37700892297526</v>
+      </c>
+      <c r="C6">
+        <v>6.500954165344448</v>
+      </c>
+      <c r="D6">
+        <v>1.569030201959678</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="B7">
-        <v>200000000000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
+        <v>13.23652674880575</v>
+      </c>
+      <c r="C7">
+        <v>7.090532340358936</v>
+      </c>
+      <c r="D7">
+        <v>2.240278207673843</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>800000000000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
+        <v>16.18405443811019</v>
+      </c>
+      <c r="C8">
+        <v>8.394964137861313</v>
+      </c>
+      <c r="D8">
+        <v>2.625876183357776</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
+        <v>18.64451527560193</v>
+      </c>
+      <c r="C9">
+        <v>8.615129075921425</v>
+      </c>
+      <c r="D9">
+        <v>3.226582762936181</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10">
+        <v>20.36283064404096</v>
+      </c>
+      <c r="C10">
+        <v>9.151036051472209</v>
+      </c>
+      <c r="D10">
+        <v>3.698909967945708</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>22.68836667019254</v>
+      </c>
+      <c r="C11">
+        <v>10.44946666940677</v>
+      </c>
+      <c r="D11">
+        <v>3.969886017024683</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>24.41031605450506</v>
+      </c>
+      <c r="C12">
+        <v>12.01869995940448</v>
+      </c>
+      <c r="D12">
+        <v>4.442165138126366</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>26.13087820236291</v>
+      </c>
+      <c r="C13">
+        <v>13.30438409999946</v>
+      </c>
+      <c r="D13">
+        <v>5.14977245141956</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>28.27605556530253</v>
+      </c>
+      <c r="C14">
+        <v>14.44655995880534</v>
+      </c>
+      <c r="D14">
+        <v>5.54260724359757</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>29.12808741850785</v>
+      </c>
+      <c r="C15">
+        <v>15.4960081110107</v>
+      </c>
+      <c r="D15">
+        <v>6.255535974760371</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>30.09313671900003</v>
+      </c>
+      <c r="C16">
+        <v>15.95674711582698</v>
+      </c>
+      <c r="D16">
+        <v>6.131586953942422</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>31.75576420145545</v>
+      </c>
+      <c r="C17">
+        <v>16.79682501162963</v>
+      </c>
+      <c r="D17">
+        <v>6.695967454817467</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>33.14806552925479</v>
+      </c>
+      <c r="C18">
+        <v>17.76650562614974</v>
+      </c>
+      <c r="D18">
+        <v>7.113376868465101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>35.33661392881196</v>
+      </c>
+      <c r="C19">
+        <v>19.49506673925919</v>
+      </c>
+      <c r="D19">
+        <v>7.453575398371928</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>36.79179948349923</v>
+      </c>
+      <c r="C20">
+        <v>20.86687588404342</v>
+      </c>
+      <c r="D20">
+        <v>7.871927553679028</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>37.94441726269806</v>
+      </c>
+      <c r="C21">
+        <v>21.18535580636206</v>
+      </c>
+      <c r="D21">
+        <v>7.874413770758849</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>40.82380652405099</v>
+      </c>
+      <c r="C22">
+        <v>22.54739779105946</v>
+      </c>
+      <c r="D22">
+        <v>8.230479393191347</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>42.68834074375907</v>
+      </c>
+      <c r="C23">
+        <v>23.5548566508513</v>
+      </c>
+      <c r="D23">
+        <v>8.701901907493696</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>44.72885766657183</v>
+      </c>
+      <c r="C24">
+        <v>24.41639565069832</v>
+      </c>
+      <c r="D24">
+        <v>9.397480716441999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>45.87400875484375</v>
+      </c>
+      <c r="C25">
+        <v>25.92223379511875</v>
+      </c>
+      <c r="D25">
+        <v>9.693826672787269</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>47.54737912012864</v>
+      </c>
+      <c r="C26">
+        <v>27.63773355636673</v>
+      </c>
+      <c r="D26">
+        <v>9.932127952208631</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>49.61393267395456</v>
+      </c>
+      <c r="C27">
+        <v>29.30337361592483</v>
+      </c>
+      <c r="D27">
+        <v>10.23177654349172</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>50.92333652750118</v>
+      </c>
+      <c r="C28">
+        <v>30.08376485431351</v>
+      </c>
+      <c r="D28">
+        <v>10.81485696703214</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>53.14875533850858</v>
+      </c>
+      <c r="C29">
+        <v>31.12915866638791</v>
+      </c>
+      <c r="D29">
+        <v>11.28060718896408</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>54.7883721245573</v>
+      </c>
+      <c r="C30">
+        <v>32.49479038208969</v>
+      </c>
+      <c r="D30">
+        <v>11.57465514821067</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="1">
         <v>30</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>50</v>
-      </c>
-      <c r="B2">
-        <v>2880000000</v>
-      </c>
-      <c r="C2">
-        <v>3000000000</v>
-      </c>
-      <c r="D2">
-        <v>11.52</v>
-      </c>
-      <c r="E2">
-        <v>23.52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>100</v>
-      </c>
-      <c r="B3">
-        <v>5760000000</v>
-      </c>
-      <c r="C3">
-        <v>6000000000</v>
-      </c>
-      <c r="D3">
-        <v>23.04</v>
-      </c>
-      <c r="E3">
-        <v>47.04</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>150</v>
-      </c>
-      <c r="B4">
-        <v>8640000000</v>
-      </c>
-      <c r="C4">
-        <v>9000000000</v>
-      </c>
-      <c r="D4">
-        <v>34.56</v>
-      </c>
-      <c r="E4">
-        <v>70.56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>200</v>
-      </c>
-      <c r="B5">
-        <v>11520000000</v>
-      </c>
-      <c r="C5">
-        <v>12000000000</v>
-      </c>
-      <c r="D5">
-        <v>46.08</v>
-      </c>
-      <c r="E5">
-        <v>94.08</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>300</v>
-      </c>
-      <c r="B6">
-        <v>17280000000</v>
-      </c>
-      <c r="C6">
-        <v>18000000000</v>
-      </c>
-      <c r="D6">
-        <v>69.12</v>
-      </c>
-      <c r="E6">
-        <v>141.12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>400</v>
-      </c>
-      <c r="B7">
-        <v>23040000000</v>
-      </c>
-      <c r="C7">
-        <v>24000000000</v>
-      </c>
-      <c r="D7">
-        <v>92.16</v>
-      </c>
-      <c r="E7">
-        <v>188.16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2">
-        <v>0.5</v>
-      </c>
-      <c r="B2">
-        <v>30</v>
-      </c>
-      <c r="C2">
-        <v>70000000000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>24</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4">
-        <v>1.5</v>
-      </c>
-      <c r="B4">
-        <v>16</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
+      <c r="B31">
+        <v>56.61335587468133</v>
+      </c>
+      <c r="C31">
+        <v>34.18256294565087</v>
+      </c>
+      <c r="D31">
+        <v>12.07730863483334</v>
       </c>
     </row>
   </sheetData>
@@ -1074,231 +2325,267 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C2">
+        <v>-0.0025</v>
+      </c>
+      <c r="D2">
+        <v>-0.005</v>
+      </c>
+      <c r="E2">
+        <v>-0.0075</v>
+      </c>
+      <c r="F2">
+        <v>-0.01</v>
+      </c>
+      <c r="G2">
+        <v>-0.0125</v>
+      </c>
+      <c r="H2">
+        <v>-0.015</v>
+      </c>
+      <c r="I2">
+        <v>-0.0175</v>
+      </c>
+      <c r="J2">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="B3">
-        <v>8</v>
+        <v>-0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="D3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>-0.01</v>
+      </c>
+      <c r="E3">
+        <v>-0.015</v>
+      </c>
+      <c r="F3">
+        <v>-0.02</v>
+      </c>
+      <c r="G3">
+        <v>-0.025</v>
+      </c>
+      <c r="H3">
+        <v>-0.03</v>
+      </c>
+      <c r="I3">
+        <v>-0.035</v>
+      </c>
+      <c r="J3">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>-0</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>-0.0125</v>
       </c>
       <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
+        <v>-0.025</v>
+      </c>
+      <c r="E4">
+        <v>-0.0375</v>
+      </c>
+      <c r="F4">
+        <v>-0.05</v>
+      </c>
+      <c r="G4">
+        <v>-0.0625</v>
+      </c>
+      <c r="H4">
+        <v>-0.075</v>
+      </c>
+      <c r="I4">
+        <v>-0.08749999999999999</v>
+      </c>
+      <c r="J4">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5">
+        <v>-0</v>
       </c>
       <c r="C5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7">
-        <v>9.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10">
-        <v>9.6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="2" width="28.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2">
-        <v>92.16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3">
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4">
-        <v>12</v>
+        <v>-0.025</v>
+      </c>
+      <c r="D5">
+        <v>-0.05</v>
+      </c>
+      <c r="E5">
+        <v>-0.075</v>
+      </c>
+      <c r="F5">
+        <v>-0.1</v>
+      </c>
+      <c r="G5">
+        <v>-0.125</v>
+      </c>
+      <c r="H5">
+        <v>-0.15</v>
+      </c>
+      <c r="I5">
+        <v>-0.175</v>
+      </c>
+      <c r="J5">
+        <v>-0.2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3">
+        <v>0.06603115471660605</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4">
+        <v>0.004171278318714422</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>0.2025691028421768</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6">
+        <v>0.2181777614275764</v>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Banking_Stress_Testing_2024.xlsx
+++ b/Banking_Stress_Testing_2024.xlsx
@@ -16,27 +16,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
-  </si>
-  <si>
-    <t>1.5%</t>
-  </si>
-  <si>
-    <t>2.0%</t>
-  </si>
-  <si>
-    <t>2.5%</t>
-  </si>
-  <si>
-    <t>3.0%</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+  <si>
+    <t>-2.0%</t>
+  </si>
+  <si>
+    <t>-1.5%</t>
+  </si>
+  <si>
+    <t>-1.0%</t>
+  </si>
+  <si>
+    <t>-0.5%</t>
+  </si>
+  <si>
+    <t>+0.0%</t>
+  </si>
+  <si>
+    <t>+0.5%</t>
+  </si>
+  <si>
+    <t>+1.0%</t>
+  </si>
+  <si>
+    <t>+1.5%</t>
+  </si>
+  <si>
+    <t>+2.0%</t>
   </si>
   <si>
     <t>1Y</t>
@@ -192,7 +198,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.0%</c:v>
+                  <c:v>-2.0%</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -227,16 +233,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-0</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0</c:v>
+                  <c:v>3.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -251,7 +257,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.5%</c:v>
+                  <c:v>-1.5%</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -286,16 +292,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-0.5</c:v>
+                  <c:v>1.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-1</c:v>
+                  <c:v>2.4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-2.5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-5</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -310,7 +316,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1.0%</c:v>
+                  <c:v>-1.0%</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -345,16 +351,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-1</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-2</c:v>
+                  <c:v>1.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-5</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-10</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -369,7 +375,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1.5%</c:v>
+                  <c:v>-0.5%</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -404,16 +410,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-1.5</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-3</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-7.5</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-15</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -428,7 +434,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2.0%</c:v>
+                  <c:v>+0.0%</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -463,16 +469,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-2</c:v>
+                  <c:v>-0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-4</c:v>
+                  <c:v>-0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-10</c:v>
+                  <c:v>-0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-20</c:v>
+                  <c:v>-0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -487,7 +493,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2.5%</c:v>
+                  <c:v>+0.5%</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -522,16 +528,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-2.5</c:v>
+                  <c:v>-0.4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-5</c:v>
+                  <c:v>-0.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-12.5</c:v>
+                  <c:v>-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-25</c:v>
+                  <c:v>-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -546,7 +552,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>3.0%</c:v>
+                  <c:v>+1.0%</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -581,16 +587,134 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>-3</c:v>
+                  <c:v>-0.8</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>-1.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Liquidity Stress'!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>+1.5%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Liquidity Stress'!$A$2:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1Y</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2Y</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5Y</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10Y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Liquidity Stress'!$I$2:$I$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>-1.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-2.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>-6</c:v>
                 </c:pt>
+                <c:pt idx="3">
+                  <c:v>-12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Liquidity Stress'!$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>+2.0%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Liquidity Stress'!$A$2:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1Y</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2Y</c:v>
+                </c:pt>
                 <c:pt idx="2">
-                  <c:v>-15</c:v>
+                  <c:v>5Y</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-30</c:v>
+                  <c:v>10Y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Liquidity Stress'!$J$2:$J$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>-1.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-3.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -701,15 +825,17 @@
     </c:title>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:v>Defaults per Round</c:v>
           </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
           <c:cat>
             <c:numRef>
               <c:f>'Contagion Simulation'!$A$2</c:f>
@@ -735,9 +861,10 @@
             </c:numRef>
           </c:val>
         </c:ser>
+        <c:marker val="1"/>
         <c:axId val="50020001"/>
         <c:axId val="50020002"/>
-      </c:barChart>
+      </c:lineChart>
       <c:catAx>
         <c:axId val="50020001"/>
         <c:scaling>
@@ -780,7 +907,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr/>
+              <a:bodyPr rot="-5400000" vert="horz"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -1171,10 +1298,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1196,109 +1323,139 @@
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2">
+        <v>1.6</v>
+      </c>
+      <c r="C2">
+        <v>1.2</v>
+      </c>
+      <c r="D2">
+        <v>0.8</v>
+      </c>
+      <c r="E2">
+        <v>0.4</v>
+      </c>
+      <c r="F2">
         <v>-0</v>
       </c>
-      <c r="C2">
-        <v>-0.5</v>
-      </c>
-      <c r="D2">
-        <v>-1</v>
-      </c>
-      <c r="E2">
-        <v>-1.5</v>
-      </c>
-      <c r="F2">
+      <c r="G2">
+        <v>-0.4</v>
+      </c>
+      <c r="H2">
+        <v>-0.8</v>
+      </c>
+      <c r="I2">
+        <v>-1.2</v>
+      </c>
+      <c r="J2">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>3.2</v>
+      </c>
+      <c r="C3">
+        <v>2.4</v>
+      </c>
+      <c r="D3">
+        <v>1.6</v>
+      </c>
+      <c r="E3">
+        <v>0.8</v>
+      </c>
+      <c r="F3">
+        <v>-0</v>
+      </c>
+      <c r="G3">
+        <v>-0.8</v>
+      </c>
+      <c r="H3">
+        <v>-1.6</v>
+      </c>
+      <c r="I3">
+        <v>-2.4</v>
+      </c>
+      <c r="J3">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>-0</v>
+      </c>
+      <c r="G4">
         <v>-2</v>
       </c>
-      <c r="G2">
-        <v>-2.5</v>
-      </c>
-      <c r="H2">
-        <v>-3</v>
+      <c r="H4">
+        <v>-4</v>
+      </c>
+      <c r="I4">
+        <v>-6</v>
+      </c>
+      <c r="J4">
+        <v>-8</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>16</v>
+      </c>
+      <c r="C5">
+        <v>12</v>
+      </c>
+      <c r="D5">
         <v>8</v>
       </c>
-      <c r="B3">
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
         <v>-0</v>
       </c>
-      <c r="C3">
-        <v>-1</v>
-      </c>
-      <c r="D3">
-        <v>-2</v>
-      </c>
-      <c r="E3">
-        <v>-3</v>
-      </c>
-      <c r="F3">
+      <c r="G5">
         <v>-4</v>
       </c>
-      <c r="G3">
-        <v>-5</v>
-      </c>
-      <c r="H3">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>-0</v>
-      </c>
-      <c r="C4">
-        <v>-2.5</v>
-      </c>
-      <c r="D4">
-        <v>-5</v>
-      </c>
-      <c r="E4">
-        <v>-7.5</v>
-      </c>
-      <c r="F4">
-        <v>-10</v>
-      </c>
-      <c r="G4">
-        <v>-12.5</v>
-      </c>
-      <c r="H4">
-        <v>-15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5">
-        <v>-0</v>
-      </c>
-      <c r="C5">
-        <v>-5</v>
-      </c>
-      <c r="D5">
-        <v>-10</v>
-      </c>
-      <c r="E5">
-        <v>-15</v>
-      </c>
-      <c r="F5">
-        <v>-20</v>
-      </c>
-      <c r="G5">
-        <v>-25</v>
-      </c>
       <c r="H5">
-        <v>-30</v>
+        <v>-8</v>
+      </c>
+      <c r="I5">
+        <v>-12</v>
+      </c>
+      <c r="J5">
+        <v>-16</v>
       </c>
     </row>
   </sheetData>
@@ -1314,30 +1471,30 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1363,7 +1520,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>0.8661761457749352</v>
@@ -1389,7 +1546,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>0.1818249672071006</v>
@@ -1415,7 +1572,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5">
         <v>0.1394938606520418</v>
@@ -1441,7 +1598,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <v>0.5924145688620425</v>
@@ -1467,7 +1624,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>0.8083973481164611</v>
@@ -1493,7 +1650,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>0.0343885211152184</v>
@@ -1529,13 +1686,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1543,10 +1700,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Banking_Stress_Testing_2024.xlsx
+++ b/Banking_Stress_Testing_2024.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t>-2.0%</t>
   </si>
@@ -87,7 +87,22 @@
     <t>New Defaults</t>
   </si>
   <si>
+    <t>Triggered Banks</t>
+  </si>
+  <si>
     <t>['SVB']</t>
+  </si>
+  <si>
+    <t>['SVB', 'Credit Suisse', 'JPM', 'BNP']</t>
+  </si>
+  <si>
+    <t>['UBS', 'JPM', 'BNP', 'Deutsche', 'SVB', 'Credit Suisse', 'HSBC']</t>
+  </si>
+  <si>
+    <t>['Credit Suisse', 'JPM', 'BNP']</t>
+  </si>
+  <si>
+    <t>['Deutsche', 'UBS', 'HSBC']</t>
   </si>
   <si>
     <t>[]</t>
@@ -831,31 +846,43 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Defaults per Round</c:v>
+            <c:v>Cumulative Defaults</c:v>
           </c:tx>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Contagion Simulation'!$A$2</c:f>
+              <c:f>'Contagion Simulation'!$A$2:$A$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Contagion Simulation'!$B$2</c:f>
+              <c:f>'Contagion Simulation'!$D$2:$D$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1500,22 +1527,22 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.9507143064099162</v>
+        <v>0.9655000144869412</v>
       </c>
       <c r="D2">
-        <v>0.7319939418114051</v>
+        <v>0.8123957592679836</v>
       </c>
       <c r="E2">
-        <v>0.5986584841970366</v>
+        <v>0.7190609389379256</v>
       </c>
       <c r="F2">
-        <v>0.1560186404424365</v>
+        <v>0.4092130483097056</v>
       </c>
       <c r="G2">
-        <v>0.1559945203362026</v>
+        <v>0.4091961642353418</v>
       </c>
       <c r="H2">
-        <v>0.05808361216819946</v>
+        <v>0.3406585285177396</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1523,25 +1550,25 @@
         <v>14</v>
       </c>
       <c r="B3">
-        <v>0.8661761457749352</v>
+        <v>0.9063233020424546</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0.7080725777960455</v>
+        <v>0.7956508044572318</v>
       </c>
       <c r="E3">
-        <v>0.02058449429580245</v>
+        <v>0.3144091460070617</v>
       </c>
       <c r="F3">
-        <v>0.9699098521619943</v>
+        <v>0.978936896513396</v>
       </c>
       <c r="G3">
-        <v>0.8324426408004217</v>
+        <v>0.8827098485602952</v>
       </c>
       <c r="H3">
-        <v>0.2123391106782762</v>
+        <v>0.4486373774747933</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1549,25 +1576,25 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>0.1818249672071006</v>
+        <v>0.4272774770449704</v>
       </c>
       <c r="C4">
-        <v>0.1834045098534338</v>
+        <v>0.4283831568974036</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.5247564316322378</v>
+        <v>0.6673295021425665</v>
       </c>
       <c r="F4">
-        <v>0.4319450186421158</v>
+        <v>0.602361513049481</v>
       </c>
       <c r="G4">
-        <v>0.2912291401980419</v>
+        <v>0.5038603981386293</v>
       </c>
       <c r="H4">
-        <v>0.6118528947223795</v>
+        <v>0.7282970263056656</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1575,25 +1602,25 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>0.1394938606520418</v>
+        <v>0.3976457024564293</v>
       </c>
       <c r="C5">
-        <v>0.2921446485352182</v>
+        <v>0.5045012539746527</v>
       </c>
       <c r="D5">
-        <v>0.3663618432936917</v>
+        <v>0.5564532903055842</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.7851759613930136</v>
+        <v>0.8496231729751095</v>
       </c>
       <c r="G5">
-        <v>0.1996737821583597</v>
+        <v>0.4397716475108518</v>
       </c>
       <c r="H5">
-        <v>0.5142344384136116</v>
+        <v>0.6599641068895281</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1601,25 +1628,25 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>0.5924145688620425</v>
+        <v>0.7146901982034297</v>
       </c>
       <c r="C6">
-        <v>0.04645041271999772</v>
+        <v>0.3325152889039984</v>
       </c>
       <c r="D6">
-        <v>0.6075448519014384</v>
+        <v>0.7252813963310069</v>
       </c>
       <c r="E6">
-        <v>0.1705241236872915</v>
+        <v>0.419366886581104</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.9488855372533332</v>
+        <v>0.9642198760773332</v>
       </c>
       <c r="H6">
-        <v>0.9656320330745594</v>
+        <v>0.9759424231521915</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1627,25 +1654,25 @@
         <v>18</v>
       </c>
       <c r="B7">
-        <v>0.8083973481164611</v>
+        <v>0.8658781436815227</v>
       </c>
       <c r="C7">
-        <v>0.3046137691733707</v>
+        <v>0.5132296384213595</v>
       </c>
       <c r="D7">
-        <v>0.09767211400638387</v>
+        <v>0.3683704798044687</v>
       </c>
       <c r="E7">
-        <v>0.6842330265121569</v>
+        <v>0.7789631185585097</v>
       </c>
       <c r="F7">
-        <v>0.4401524937396013</v>
+        <v>0.6081067456177209</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0.4951769101112702</v>
+        <v>0.6466238370778891</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1653,22 +1680,22 @@
         <v>19</v>
       </c>
       <c r="B8">
-        <v>0.0343885211152184</v>
+        <v>0.3240719647806529</v>
       </c>
       <c r="C8">
-        <v>0.9093204020787821</v>
+        <v>0.9365242814551474</v>
       </c>
       <c r="D8">
-        <v>0.2587799816000169</v>
+        <v>0.4811459871200118</v>
       </c>
       <c r="E8">
-        <v>0.662522284353982</v>
+        <v>0.7637655990477873</v>
       </c>
       <c r="F8">
-        <v>0.311711076089411</v>
+        <v>0.5181977532625877</v>
       </c>
       <c r="G8">
-        <v>0.5200680211778108</v>
+        <v>0.6640476148244675</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1681,10 +1708,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -1694,16 +1721,50 @@
       <c r="C1" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Banking_Stress_Testing_2024.xlsx
+++ b/Banking_Stress_Testing_2024.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
   <si>
     <t>-2.0%</t>
   </si>
@@ -81,31 +81,10 @@
     <t>Round</t>
   </si>
   <si>
-    <t>Defaults</t>
-  </si>
-  <si>
     <t>New Defaults</t>
   </si>
   <si>
-    <t>Triggered Banks</t>
-  </si>
-  <si>
-    <t>['SVB']</t>
-  </si>
-  <si>
-    <t>['SVB', 'Credit Suisse', 'JPM', 'BNP']</t>
-  </si>
-  <si>
-    <t>['UBS', 'JPM', 'BNP', 'Deutsche', 'SVB', 'Credit Suisse', 'HSBC']</t>
-  </si>
-  <si>
-    <t>['Credit Suisse', 'JPM', 'BNP']</t>
-  </si>
-  <si>
-    <t>['Deutsche', 'UBS', 'HSBC']</t>
-  </si>
-  <si>
-    <t>[]</t>
+    <t>Cumulative Defaults</t>
   </si>
 </sst>
 </file>
@@ -848,41 +827,26 @@
           <c:tx>
             <c:v>Cumulative Defaults</c:v>
           </c:tx>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'Contagion Simulation'!$A$2:$A$4</c:f>
+              <c:f>'Contagion Simulation'!$A$2</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Contagion Simulation'!$D$2:$D$4</c:f>
+              <c:f>'Contagion Simulation'!$C$2</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7</c:v>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1527,22 +1491,22 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.9655000144869412</v>
+        <v>0.2015171140968154</v>
       </c>
       <c r="D2">
-        <v>0.8123957592679836</v>
+        <v>0.3472299500874105</v>
       </c>
       <c r="E2">
-        <v>0.7190609389379256</v>
+        <v>0.3276977356218537</v>
       </c>
       <c r="F2">
-        <v>0.4092130483097056</v>
+        <v>0.2024851416253264</v>
       </c>
       <c r="G2">
-        <v>0.4091961642353418</v>
+        <v>0.19915236922909</v>
       </c>
       <c r="H2">
-        <v>0.3406585285177396</v>
+        <v>0.3119542018978421</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1550,25 +1514,25 @@
         <v>14</v>
       </c>
       <c r="B3">
-        <v>0.9063233020424546</v>
+        <v>0.3515084983910086</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0.7956508044572318</v>
+        <v>0.3294494716354866</v>
       </c>
       <c r="E3">
-        <v>0.3144091460070617</v>
+        <v>0.121372929912071</v>
       </c>
       <c r="F3">
-        <v>0.978936896513396</v>
+        <v>0.1803461968899578</v>
       </c>
       <c r="G3">
-        <v>0.8827098485602952</v>
+        <v>0.2526789777827141</v>
       </c>
       <c r="H3">
-        <v>0.4486373774747933</v>
+        <v>0.05441336795621621</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1576,25 +1540,25 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>0.4272774770449704</v>
+        <v>0.1010946905290184</v>
       </c>
       <c r="C4">
-        <v>0.4283831568974036</v>
+        <v>0.1630183379481444</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.6673295021425665</v>
+        <v>0.1790563183236937</v>
       </c>
       <c r="F4">
-        <v>0.602361513049481</v>
+        <v>0.1445652783407431</v>
       </c>
       <c r="G4">
-        <v>0.5038603981386293</v>
+        <v>0.1104968301443956</v>
       </c>
       <c r="H4">
-        <v>0.7282970263056656</v>
+        <v>0.2947343272433132</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1602,25 +1566,25 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>0.3976457024564293</v>
+        <v>0.2139256176738007</v>
       </c>
       <c r="C5">
-        <v>0.5045012539746527</v>
+        <v>0.2233568159407045</v>
       </c>
       <c r="D5">
-        <v>0.5564532903055842</v>
+        <v>0.1231950508574958</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.8496231729751095</v>
+        <v>0.2406165268620911</v>
       </c>
       <c r="G5">
-        <v>0.4397716475108518</v>
+        <v>0.1259193844236645</v>
       </c>
       <c r="H5">
-        <v>0.6599641068895281</v>
+        <v>0.1709034863175575</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1628,25 +1592,25 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>0.7146901982034297</v>
+        <v>0.1773627692521712</v>
       </c>
       <c r="C6">
-        <v>0.3325152889039984</v>
+        <v>0.1866358863576689</v>
       </c>
       <c r="D6">
-        <v>0.7252813963310069</v>
+        <v>0.1859150159252627</v>
       </c>
       <c r="E6">
-        <v>0.419366886581104</v>
+        <v>0.3863392269503714</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0.9642198760773332</v>
+        <v>0.1319315490472855</v>
       </c>
       <c r="H6">
-        <v>0.9759424231521915</v>
+        <v>0.2136891601754855</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1654,25 +1618,25 @@
         <v>18</v>
       </c>
       <c r="B7">
-        <v>0.8658781436815227</v>
+        <v>0.1300728527031288</v>
       </c>
       <c r="C7">
-        <v>0.5132296384213595</v>
+        <v>0.2397120135642348</v>
       </c>
       <c r="D7">
-        <v>0.3683704798044687</v>
+        <v>0.09428366113132033</v>
       </c>
       <c r="E7">
-        <v>0.7789631185585097</v>
+        <v>0.07876617812509668</v>
       </c>
       <c r="F7">
-        <v>0.6081067456177209</v>
+        <v>0.2511810049407988</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0.6466238370778891</v>
+        <v>0.1543054564095856</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1680,22 +1644,22 @@
         <v>19</v>
       </c>
       <c r="B8">
-        <v>0.3240719647806529</v>
+        <v>0.2260355714508724</v>
       </c>
       <c r="C8">
-        <v>0.9365242814551474</v>
+        <v>0.185759832092432</v>
       </c>
       <c r="D8">
-        <v>0.4811459871200118</v>
+        <v>0.119926850363024</v>
       </c>
       <c r="E8">
-        <v>0.7637655990477873</v>
+        <v>0.1067676110669135</v>
       </c>
       <c r="F8">
-        <v>0.5181977532625877</v>
+        <v>0.1808058513410825</v>
       </c>
       <c r="G8">
-        <v>0.6640476148244675</v>
+        <v>0.3798208893728503</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1708,10 +1672,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -1721,50 +1685,16 @@
       <c r="C1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>23</v>
-      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
